--- a/data/raw/PSY_SUD_genetic_corr.xlsx
+++ b/data/raw/PSY_SUD_genetic_corr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giaco\Desktop\Git_META\META\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F257572-0C44-4508-B4E8-7AD29317D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D736ADE-332F-4453-AFCB-53A529FB4AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>AN</t>
   </si>
@@ -42,9 +42,6 @@
     <t>ADHD</t>
   </si>
   <si>
-    <t>PTSD</t>
-  </si>
-  <si>
     <t>NIC</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>0.581</t>
   </si>
   <si>
-    <t>0.538</t>
-  </si>
-  <si>
     <t>0.42</t>
   </si>
   <si>
@@ -99,9 +93,6 @@
     <t>0.409</t>
   </si>
   <si>
-    <t>0.452</t>
-  </si>
-  <si>
     <t>0.447</t>
   </si>
   <si>
@@ -120,9 +111,6 @@
     <t>0.497</t>
   </si>
   <si>
-    <t>0.48</t>
-  </si>
-  <si>
     <t>0.458</t>
   </si>
   <si>
@@ -138,9 +126,6 @@
     <t>0.418</t>
   </si>
   <si>
-    <t>0.498</t>
-  </si>
-  <si>
     <t>0.491</t>
   </si>
   <si>
@@ -150,13 +135,13 @@
     <t>OPI</t>
   </si>
   <si>
-    <t>COC</t>
-  </si>
-  <si>
     <t>MDD</t>
   </si>
   <si>
     <t>BD</t>
+  </si>
+  <si>
+    <t>CAN</t>
   </si>
 </sst>
 </file>
@@ -524,22 +509,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -547,16 +532,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -564,16 +549,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -581,33 +566,33 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -615,16 +600,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -632,51 +617,41 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
@@ -699,13 +674,6 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
